--- a/DetalleXDocente20232.xlsx
+++ b/DetalleXDocente20232.xlsx
@@ -1506,22 +1506,22 @@
         <v>131</v>
       </c>
       <c r="D20">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" s="1">
-        <v>96.8</v>
+        <v>97</v>
       </c>
       <c r="H20" s="1">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I20" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>131</v>
       </c>
       <c r="D21">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E21">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1556,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1678,19 +1678,19 @@
         <v>121</v>
       </c>
       <c r="D25">
+        <v>142</v>
+      </c>
+      <c r="E25">
         <v>138</v>
-      </c>
-      <c r="E25">
-        <v>134</v>
       </c>
       <c r="F25">
         <v>4</v>
       </c>
       <c r="G25" s="1">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="H25" s="1">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I25" s="2">
         <v>8.300000000000001</v>
@@ -1713,22 +1713,22 @@
         <v>133</v>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F26">
         <v>4</v>
       </c>
       <c r="G26" s="1">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H26" s="1">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="I26" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1745,22 +1745,22 @@
         <v>121</v>
       </c>
       <c r="D27">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F27">
         <v>4</v>
       </c>
       <c r="G27" s="1">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H27" s="1">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="I27" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1850,10 +1850,10 @@
         <v>131</v>
       </c>
       <c r="D30">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E30">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1882,19 +1882,19 @@
         <v>121</v>
       </c>
       <c r="D31">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E31">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F31">
         <v>5</v>
       </c>
       <c r="G31" s="1">
-        <v>95.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H31" s="1">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I31" s="2">
         <v>8.5</v>
@@ -2538,22 +2538,22 @@
         <v>133</v>
       </c>
       <c r="D50">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E50">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F50">
         <v>6</v>
       </c>
       <c r="G50" s="1">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="H50" s="1">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="I50" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -2570,19 +2570,19 @@
         <v>121</v>
       </c>
       <c r="D51">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E51">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F51">
         <v>25</v>
       </c>
       <c r="G51" s="1">
-        <v>77.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H51" s="1">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="I51" s="2">
         <v>7.1</v>
@@ -2815,22 +2815,22 @@
         <v>133</v>
       </c>
       <c r="D58">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E58">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F58">
         <v>5</v>
       </c>
       <c r="G58" s="1">
-        <v>64.3</v>
+        <v>66.7</v>
       </c>
       <c r="H58" s="1">
-        <v>35.7</v>
+        <v>33.3</v>
       </c>
       <c r="I58" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -2847,19 +2847,19 @@
         <v>121</v>
       </c>
       <c r="D59">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E59">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F59">
         <v>73</v>
       </c>
       <c r="G59" s="1">
-        <v>64.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="H59" s="1">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="I59" s="2">
         <v>6.5</v>
@@ -5060,22 +5060,22 @@
         <v>133</v>
       </c>
       <c r="D123">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E123">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F123">
         <v>4</v>
       </c>
       <c r="G123" s="1">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H123" s="1">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="I123" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -5092,19 +5092,19 @@
         <v>121</v>
       </c>
       <c r="D124">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E124">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F124">
         <v>45</v>
       </c>
       <c r="G124" s="1">
-        <v>65.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H124" s="1">
-        <v>34.9</v>
+        <v>34.6</v>
       </c>
       <c r="I124" s="2">
         <v>6.5</v>
@@ -5474,22 +5474,22 @@
         <v>133</v>
       </c>
       <c r="D135">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E135">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F135">
         <v>4</v>
       </c>
       <c r="G135" s="1">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H135" s="1">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="I135" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -5506,19 +5506,19 @@
         <v>121</v>
       </c>
       <c r="D136">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E136">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F136">
         <v>23</v>
       </c>
       <c r="G136" s="1">
-        <v>85.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="H136" s="1">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="I136" s="2">
         <v>8</v>
@@ -5984,10 +5984,10 @@
         <v>131</v>
       </c>
       <c r="D150">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E150">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -6016,10 +6016,10 @@
         <v>121</v>
       </c>
       <c r="D151">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E151">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -6809,19 +6809,19 @@
         <v>131</v>
       </c>
       <c r="D174">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E174">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F174">
         <v>1</v>
       </c>
       <c r="G174" s="1">
-        <v>96.8</v>
+        <v>97</v>
       </c>
       <c r="H174" s="1">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I174" s="2">
         <v>8.5</v>
@@ -6911,19 +6911,19 @@
         <v>121</v>
       </c>
       <c r="D177">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E177">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F177">
         <v>25</v>
       </c>
       <c r="G177" s="1">
-        <v>86.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="H177" s="1">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="I177" s="2">
         <v>7.8</v>
@@ -7296,22 +7296,22 @@
         <v>133</v>
       </c>
       <c r="D188">
+        <v>15</v>
+      </c>
+      <c r="E188">
         <v>14</v>
-      </c>
-      <c r="E188">
-        <v>13</v>
       </c>
       <c r="F188">
         <v>1</v>
       </c>
       <c r="G188" s="1">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="H188" s="1">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I188" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J188">
         <v>0</v>
@@ -7328,19 +7328,19 @@
         <v>121</v>
       </c>
       <c r="D189">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E189">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F189">
         <v>78</v>
       </c>
       <c r="G189" s="1">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H189" s="1">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="I189" s="2">
         <v>7</v>
@@ -10223,10 +10223,10 @@
         <v>131</v>
       </c>
       <c r="D273">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E273">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F273">
         <v>0</v>
@@ -10325,19 +10325,19 @@
         <v>121</v>
       </c>
       <c r="D276">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E276">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F276">
         <v>19</v>
       </c>
       <c r="G276" s="1">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H276" s="1">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="I276" s="2">
         <v>7.7</v>
@@ -11185,7 +11185,7 @@
         <v>13.8</v>
       </c>
       <c r="I7" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -11616,19 +11616,19 @@
         <v>131</v>
       </c>
       <c r="D20">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" s="1">
-        <v>96.8</v>
+        <v>97</v>
       </c>
       <c r="H20" s="1">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I20" s="2">
         <v>8.300000000000001</v>
@@ -11651,10 +11651,10 @@
         <v>131</v>
       </c>
       <c r="D21">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E21">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -11788,19 +11788,19 @@
         <v>121</v>
       </c>
       <c r="D25">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E25">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F25">
         <v>15</v>
       </c>
       <c r="G25" s="1">
-        <v>89.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="I25" s="2">
         <v>7.4</v>
@@ -11823,22 +11823,22 @@
         <v>133</v>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F26">
         <v>2</v>
       </c>
       <c r="G26" s="1">
-        <v>85.7</v>
+        <v>86.7</v>
       </c>
       <c r="H26" s="1">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="I26" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -11855,22 +11855,22 @@
         <v>121</v>
       </c>
       <c r="D27">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F27">
         <v>2</v>
       </c>
       <c r="G27" s="1">
-        <v>85.7</v>
+        <v>86.7</v>
       </c>
       <c r="H27" s="1">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="I27" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -11960,10 +11960,10 @@
         <v>131</v>
       </c>
       <c r="D30">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E30">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -11992,10 +11992,10 @@
         <v>121</v>
       </c>
       <c r="D31">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E31">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F31">
         <v>3</v>
@@ -12648,22 +12648,22 @@
         <v>133</v>
       </c>
       <c r="D50">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E50">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F50">
         <v>4</v>
       </c>
       <c r="G50" s="1">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H50" s="1">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="I50" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -12680,22 +12680,22 @@
         <v>121</v>
       </c>
       <c r="D51">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E51">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F51">
         <v>21</v>
       </c>
       <c r="G51" s="1">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H51" s="1">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="I51" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -12788,25 +12788,25 @@
         <v>31</v>
       </c>
       <c r="E54">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F54">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G54" s="1">
-        <v>74.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H54" s="1">
-        <v>25.8</v>
+        <v>22.6</v>
       </c>
       <c r="I54" s="2">
         <v>7.5</v>
       </c>
       <c r="J54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1">
-        <v>3.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -12925,28 +12925,28 @@
         <v>133</v>
       </c>
       <c r="D58">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E58">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G58" s="1">
-        <v>71.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="H58" s="1">
-        <v>28.6</v>
+        <v>20</v>
       </c>
       <c r="I58" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1">
-        <v>7.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -12957,28 +12957,28 @@
         <v>121</v>
       </c>
       <c r="D59">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E59">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F59">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G59" s="1">
-        <v>71.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="H59" s="1">
-        <v>28.6</v>
+        <v>27.5</v>
       </c>
       <c r="I59" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J59">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -14634,7 +14634,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -15170,22 +15170,22 @@
         <v>133</v>
       </c>
       <c r="D123">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E123">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F123">
         <v>4</v>
       </c>
       <c r="G123" s="1">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H123" s="1">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="I123" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -15202,22 +15202,22 @@
         <v>121</v>
       </c>
       <c r="D124">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E124">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F124">
         <v>44</v>
       </c>
       <c r="G124" s="1">
-        <v>65.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="H124" s="1">
-        <v>34.1</v>
+        <v>33.8</v>
       </c>
       <c r="I124" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -15584,22 +15584,22 @@
         <v>133</v>
       </c>
       <c r="D135">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E135">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F135">
         <v>5</v>
       </c>
       <c r="G135" s="1">
-        <v>64.3</v>
+        <v>66.7</v>
       </c>
       <c r="H135" s="1">
-        <v>35.7</v>
+        <v>33.3</v>
       </c>
       <c r="I135" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -15616,19 +15616,19 @@
         <v>121</v>
       </c>
       <c r="D136">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E136">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F136">
         <v>24</v>
       </c>
       <c r="G136" s="1">
-        <v>84.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="H136" s="1">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="I136" s="2">
         <v>7.6</v>
@@ -16094,10 +16094,10 @@
         <v>131</v>
       </c>
       <c r="D150">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E150">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -16126,10 +16126,10 @@
         <v>121</v>
       </c>
       <c r="D151">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E151">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -16919,10 +16919,10 @@
         <v>131</v>
       </c>
       <c r="D174">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E174">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F174">
         <v>0</v>
@@ -16934,7 +16934,7 @@
         <v>0</v>
       </c>
       <c r="I174" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J174">
         <v>0</v>
@@ -17021,22 +17021,22 @@
         <v>121</v>
       </c>
       <c r="D177">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E177">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F177">
         <v>23</v>
       </c>
       <c r="G177" s="1">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="H177" s="1">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="I177" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J177">
         <v>0</v>
@@ -17406,22 +17406,22 @@
         <v>133</v>
       </c>
       <c r="D188">
+        <v>15</v>
+      </c>
+      <c r="E188">
         <v>14</v>
-      </c>
-      <c r="E188">
-        <v>13</v>
       </c>
       <c r="F188">
         <v>1</v>
       </c>
       <c r="G188" s="1">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="H188" s="1">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I188" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J188">
         <v>0</v>
@@ -17438,22 +17438,22 @@
         <v>121</v>
       </c>
       <c r="D189">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E189">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F189">
         <v>49</v>
       </c>
       <c r="G189" s="1">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="H189" s="1">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="I189" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J189">
         <v>0</v>
@@ -17902,7 +17902,7 @@
         <v>6.9</v>
       </c>
       <c r="I202" s="2">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="J202">
         <v>0</v>
@@ -17972,7 +17972,7 @@
         <v>29</v>
       </c>
       <c r="I204" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J204">
         <v>0</v>
@@ -18007,7 +18007,7 @@
         <v>19.4</v>
       </c>
       <c r="I205" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J205">
         <v>0</v>
@@ -18039,7 +18039,7 @@
         <v>18.4</v>
       </c>
       <c r="I206" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J206">
         <v>0</v>
@@ -20333,10 +20333,10 @@
         <v>131</v>
       </c>
       <c r="D273">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E273">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F273">
         <v>0</v>
@@ -20435,19 +20435,19 @@
         <v>121</v>
       </c>
       <c r="D276">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E276">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F276">
         <v>17</v>
       </c>
       <c r="G276" s="1">
-        <v>90.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="H276" s="1">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I276" s="2">
         <v>8</v>
@@ -21111,25 +21111,25 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="H2" s="1">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="I2" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -21146,25 +21146,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>85.7</v>
+        <v>90.5</v>
       </c>
       <c r="H3" s="1">
-        <v>14.3</v>
+        <v>9.5</v>
       </c>
       <c r="I3" s="2">
         <v>7.5</v>
       </c>
       <c r="J3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -21193,13 +21193,13 @@
         <v>3.3</v>
       </c>
       <c r="I4" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -21228,13 +21228,13 @@
         <v>6.7</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -21260,13 +21260,13 @@
         <v>9</v>
       </c>
       <c r="I6" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -21283,25 +21283,25 @@
         <v>29</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -21318,25 +21318,25 @@
         <v>42</v>
       </c>
       <c r="E8">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>88.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>11.9</v>
+        <v>7.1</v>
       </c>
       <c r="I8" s="2">
         <v>8</v>
       </c>
       <c r="J8">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -21353,25 +21353,25 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="I9" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J9">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -21388,25 +21388,25 @@
         <v>45</v>
       </c>
       <c r="E10">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>77.8</v>
+        <v>86.7</v>
       </c>
       <c r="H10" s="1">
-        <v>22.2</v>
+        <v>13.3</v>
       </c>
       <c r="I10" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J10">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -21423,25 +21423,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>83.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -21458,25 +21458,25 @@
         <v>38</v>
       </c>
       <c r="E12">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>92.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="H12" s="1">
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
       <c r="I12" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J12">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -21490,25 +21490,25 @@
         <v>220</v>
       </c>
       <c r="E13">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="F13">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
-        <v>86.8</v>
+        <v>94.5</v>
       </c>
       <c r="H13" s="1">
-        <v>13.2</v>
+        <v>5.5</v>
       </c>
       <c r="I13" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J13">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -21537,10 +21537,10 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -21566,10 +21566,10 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -21586,25 +21586,25 @@
         <v>39</v>
       </c>
       <c r="E16">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F16">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>66.7</v>
+        <v>92.3</v>
       </c>
       <c r="H16" s="1">
-        <v>33.3</v>
+        <v>7.7</v>
       </c>
       <c r="I16" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -21621,25 +21621,25 @@
         <v>39</v>
       </c>
       <c r="E17">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F17">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G17" s="1">
-        <v>69.2</v>
+        <v>92.3</v>
       </c>
       <c r="H17" s="1">
-        <v>30.8</v>
+        <v>7.7</v>
       </c>
       <c r="I17" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J17">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -21656,25 +21656,25 @@
         <v>38</v>
       </c>
       <c r="E18">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>84.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>15.8</v>
+        <v>2.6</v>
       </c>
       <c r="I18" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J18">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -21688,25 +21688,25 @@
         <v>116</v>
       </c>
       <c r="E19">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="F19">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G19" s="1">
-        <v>73.3</v>
+        <v>94</v>
       </c>
       <c r="H19" s="1">
-        <v>26.7</v>
+        <v>6</v>
       </c>
       <c r="I19" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J19">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -21720,28 +21720,28 @@
         <v>131</v>
       </c>
       <c r="D20">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E20">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
         <v>8.5</v>
       </c>
       <c r="J20">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -21755,10 +21755,10 @@
         <v>131</v>
       </c>
       <c r="D21">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E21">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -21770,13 +21770,13 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J21">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -21793,25 +21793,25 @@
         <v>26</v>
       </c>
       <c r="E22">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F22">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>73.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="H22" s="1">
-        <v>26.9</v>
+        <v>3.8</v>
       </c>
       <c r="I22" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J22">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -21828,25 +21828,25 @@
         <v>25</v>
       </c>
       <c r="E23">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
         <v>7.4</v>
       </c>
       <c r="J23">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -21863,25 +21863,25 @@
         <v>25</v>
       </c>
       <c r="E24">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J24">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -21892,28 +21892,28 @@
         <v>121</v>
       </c>
       <c r="D25">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E25">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="F25">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>89.09999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="H25" s="1">
-        <v>10.9</v>
+        <v>0.7</v>
       </c>
       <c r="I25" s="2">
         <v>8</v>
       </c>
       <c r="J25">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -21927,28 +21927,28 @@
         <v>133</v>
       </c>
       <c r="D26">
+        <v>15</v>
+      </c>
+      <c r="E26">
         <v>14</v>
       </c>
-      <c r="E26">
-        <v>12</v>
-      </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1">
-        <v>85.7</v>
+        <v>93.3</v>
       </c>
       <c r="H26" s="1">
-        <v>14.3</v>
+        <v>6.7</v>
       </c>
       <c r="I26" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J26">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -21959,28 +21959,28 @@
         <v>121</v>
       </c>
       <c r="D27">
+        <v>15</v>
+      </c>
+      <c r="E27">
         <v>14</v>
       </c>
-      <c r="E27">
-        <v>12</v>
-      </c>
       <c r="F27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="1">
-        <v>85.7</v>
+        <v>93.3</v>
       </c>
       <c r="H27" s="1">
-        <v>14.3</v>
+        <v>6.7</v>
       </c>
       <c r="I27" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J27">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -21997,25 +21997,25 @@
         <v>35</v>
       </c>
       <c r="E28">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" s="1">
-        <v>97.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H28" s="1">
-        <v>2.9</v>
+        <v>8.6</v>
       </c>
       <c r="I28" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J28">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -22032,25 +22032,25 @@
         <v>45</v>
       </c>
       <c r="E29">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>95.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H29" s="1">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J29">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -22064,10 +22064,10 @@
         <v>131</v>
       </c>
       <c r="D30">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E30">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -22082,10 +22082,10 @@
         <v>9.4</v>
       </c>
       <c r="J30">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -22096,10 +22096,10 @@
         <v>121</v>
       </c>
       <c r="D31">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E31">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F31">
         <v>3</v>
@@ -22114,10 +22114,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J31">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -22134,25 +22134,25 @@
         <v>30</v>
       </c>
       <c r="E32">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F32">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G32" s="1">
-        <v>56.7</v>
+        <v>80</v>
       </c>
       <c r="H32" s="1">
-        <v>43.3</v>
+        <v>20</v>
       </c>
       <c r="I32" s="2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J32">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -22169,25 +22169,25 @@
         <v>29</v>
       </c>
       <c r="E33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G33" s="1">
-        <v>82.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>17.2</v>
+        <v>3.4</v>
       </c>
       <c r="I33" s="2">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J33">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -22204,25 +22204,25 @@
         <v>23</v>
       </c>
       <c r="E34">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G34" s="1">
-        <v>82.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="H34" s="1">
-        <v>17.4</v>
+        <v>4.3</v>
       </c>
       <c r="I34" s="2">
         <v>7.7</v>
       </c>
       <c r="J34">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -22239,25 +22239,25 @@
         <v>33</v>
       </c>
       <c r="E35">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F35">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G35" s="1">
-        <v>57.6</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H35" s="1">
-        <v>42.4</v>
+        <v>6.1</v>
       </c>
       <c r="I35" s="2">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="J35">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -22274,25 +22274,25 @@
         <v>12</v>
       </c>
       <c r="E36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36" s="1">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="H36" s="1">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="I36" s="2">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="J36">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -22306,25 +22306,25 @@
         <v>127</v>
       </c>
       <c r="E37">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="F37">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="G37" s="1">
-        <v>68.5</v>
+        <v>89.8</v>
       </c>
       <c r="H37" s="1">
-        <v>31.5</v>
+        <v>10.2</v>
       </c>
       <c r="I37" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J37">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -22353,13 +22353,13 @@
         <v>4</v>
       </c>
       <c r="I38" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J38">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -22388,10 +22388,10 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -22420,13 +22420,13 @@
         <v>0</v>
       </c>
       <c r="I40" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J40">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -22455,10 +22455,10 @@
         <v>8</v>
       </c>
       <c r="J41">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -22475,25 +22475,25 @@
         <v>31</v>
       </c>
       <c r="E42">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G42" s="1">
-        <v>87.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="H42" s="1">
-        <v>12.9</v>
+        <v>6.5</v>
       </c>
       <c r="I42" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J42">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -22510,25 +22510,25 @@
         <v>31</v>
       </c>
       <c r="E43">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F43">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G43" s="1">
-        <v>83.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="H43" s="1">
-        <v>16.1</v>
+        <v>3.2</v>
       </c>
       <c r="I43" s="2">
         <v>7.2</v>
       </c>
       <c r="J43">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -22545,25 +22545,25 @@
         <v>23</v>
       </c>
       <c r="E44">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G44" s="1">
-        <v>78.3</v>
+        <v>95.7</v>
       </c>
       <c r="H44" s="1">
-        <v>21.7</v>
+        <v>4.3</v>
       </c>
       <c r="I44" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J44">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -22577,25 +22577,25 @@
         <v>85</v>
       </c>
       <c r="E45">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F45">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G45" s="1">
-        <v>83.5</v>
+        <v>95.3</v>
       </c>
       <c r="H45" s="1">
-        <v>16.5</v>
+        <v>4.7</v>
       </c>
       <c r="I45" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J45">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -22612,25 +22612,25 @@
         <v>26</v>
       </c>
       <c r="E46">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" s="1">
+        <v>96.2</v>
+      </c>
+      <c r="H46" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="I46" s="2">
         <v>7</v>
       </c>
-      <c r="G46" s="1">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="H46" s="1">
-        <v>26.9</v>
-      </c>
-      <c r="I46" s="2">
-        <v>6.9</v>
-      </c>
       <c r="J46">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -22647,25 +22647,25 @@
         <v>32</v>
       </c>
       <c r="E47">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F47">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G47" s="1">
-        <v>75</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H47" s="1">
-        <v>25</v>
+        <v>3.1</v>
       </c>
       <c r="I47" s="2">
         <v>6.9</v>
       </c>
       <c r="J47">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -22694,13 +22694,13 @@
         <v>6.7</v>
       </c>
       <c r="I48" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J48">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -22717,25 +22717,25 @@
         <v>25</v>
       </c>
       <c r="E49">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H49" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I49" s="2">
         <v>7.8</v>
       </c>
       <c r="J49">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -22749,28 +22749,28 @@
         <v>133</v>
       </c>
       <c r="D50">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E50">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G50" s="1">
-        <v>71.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="H50" s="1">
-        <v>28.6</v>
+        <v>13.3</v>
       </c>
       <c r="I50" s="2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="J50">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -22781,28 +22781,28 @@
         <v>121</v>
       </c>
       <c r="D51">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E51">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="F51">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G51" s="1">
-        <v>81.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H51" s="1">
-        <v>18.8</v>
+        <v>4.4</v>
       </c>
       <c r="I51" s="2">
         <v>7.3</v>
       </c>
       <c r="J51">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -22819,25 +22819,25 @@
         <v>25</v>
       </c>
       <c r="E52">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F52">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G52" s="1">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="H52" s="1">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I52" s="2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J52">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -22854,25 +22854,25 @@
         <v>39</v>
       </c>
       <c r="E53">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F53">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G53" s="1">
-        <v>71.8</v>
+        <v>89.7</v>
       </c>
       <c r="H53" s="1">
-        <v>28.2</v>
+        <v>10.3</v>
       </c>
       <c r="I53" s="2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="J53">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K53" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -22889,25 +22889,25 @@
         <v>31</v>
       </c>
       <c r="E54">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F54">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G54" s="1">
-        <v>77.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="H54" s="1">
-        <v>22.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I54" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J54">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -22924,25 +22924,25 @@
         <v>35</v>
       </c>
       <c r="E55">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F55">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G55" s="1">
-        <v>68.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H55" s="1">
-        <v>31.4</v>
+        <v>17.1</v>
       </c>
       <c r="I55" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J55">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K55" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -22959,25 +22959,25 @@
         <v>24</v>
       </c>
       <c r="E56">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F56">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G56" s="1">
-        <v>58.3</v>
+        <v>95.8</v>
       </c>
       <c r="H56" s="1">
-        <v>41.7</v>
+        <v>4.2</v>
       </c>
       <c r="I56" s="2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J56">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K56" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -22994,25 +22994,25 @@
         <v>38</v>
       </c>
       <c r="E57">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G57" s="1">
-        <v>89.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H57" s="1">
-        <v>10.5</v>
+        <v>2.6</v>
       </c>
       <c r="I57" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J57">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K57" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -23026,28 +23026,28 @@
         <v>133</v>
       </c>
       <c r="D58">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E58">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F58">
         <v>3</v>
       </c>
       <c r="G58" s="1">
-        <v>78.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="H58" s="1">
-        <v>21.4</v>
+        <v>20</v>
       </c>
       <c r="I58" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J58">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -23058,28 +23058,28 @@
         <v>121</v>
       </c>
       <c r="D59">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E59">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="F59">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="G59" s="1">
-        <v>72.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H59" s="1">
-        <v>27.7</v>
+        <v>12.1</v>
       </c>
       <c r="I59" s="2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="J59">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="K59" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -23096,25 +23096,25 @@
         <v>38</v>
       </c>
       <c r="E60">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F60">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G60" s="1">
-        <v>84.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H60" s="1">
-        <v>15.8</v>
+        <v>2.6</v>
       </c>
       <c r="I60" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J60">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K60" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -23131,25 +23131,25 @@
         <v>29</v>
       </c>
       <c r="E61">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="G61" s="1">
-        <v>93.09999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="H61" s="1">
-        <v>6.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I61" s="2">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="J61">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -23181,10 +23181,10 @@
         <v>9.6</v>
       </c>
       <c r="J62">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -23201,25 +23201,25 @@
         <v>31</v>
       </c>
       <c r="E63">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G63" s="1">
-        <v>83.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="H63" s="1">
-        <v>16.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I63" s="2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="J63">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K63" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -23236,25 +23236,25 @@
         <v>38</v>
       </c>
       <c r="E64">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64" s="1">
-        <v>97.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="H64" s="1">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="I64" s="2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J64">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K64" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -23283,13 +23283,13 @@
         <v>5.3</v>
       </c>
       <c r="I65" s="2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J65">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K65" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -23318,13 +23318,13 @@
         <v>5.3</v>
       </c>
       <c r="I66" s="2">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J66">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K66" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -23338,25 +23338,25 @@
         <v>254</v>
       </c>
       <c r="E67">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="F67">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G67" s="1">
-        <v>92.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H67" s="1">
-        <v>7.5</v>
+        <v>15.4</v>
       </c>
       <c r="I67" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J67">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="K67" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -23373,25 +23373,25 @@
         <v>29</v>
       </c>
       <c r="E68">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F68">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G68" s="1">
-        <v>69</v>
+        <v>86.2</v>
       </c>
       <c r="H68" s="1">
-        <v>31</v>
+        <v>13.8</v>
       </c>
       <c r="I68" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J68">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K68" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -23408,25 +23408,25 @@
         <v>32</v>
       </c>
       <c r="E69">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G69" s="1">
-        <v>90.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H69" s="1">
-        <v>9.4</v>
+        <v>3.1</v>
       </c>
       <c r="I69" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J69">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -23440,25 +23440,25 @@
         <v>61</v>
       </c>
       <c r="E70">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F70">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G70" s="1">
-        <v>80.3</v>
+        <v>91.8</v>
       </c>
       <c r="H70" s="1">
-        <v>19.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I70" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J70">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K70" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -23475,25 +23475,25 @@
         <v>25</v>
       </c>
       <c r="E71">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F71">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G71" s="1">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="H71" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I71" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J71">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K71" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -23522,13 +23522,13 @@
         <v>4.2</v>
       </c>
       <c r="I72" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J72">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K72" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -23545,25 +23545,25 @@
         <v>30</v>
       </c>
       <c r="E73">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F73">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G73" s="1">
-        <v>86.7</v>
+        <v>76.7</v>
       </c>
       <c r="H73" s="1">
-        <v>13.3</v>
+        <v>23.3</v>
       </c>
       <c r="I73" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J73">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -23592,13 +23592,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J74">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K74" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -23627,13 +23627,13 @@
         <v>4.3</v>
       </c>
       <c r="I75" s="2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J75">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K75" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -23659,13 +23659,13 @@
         <v>9</v>
       </c>
       <c r="I76" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J76">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="K76" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -23682,25 +23682,25 @@
         <v>25</v>
       </c>
       <c r="E77">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F77">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G77" s="1">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="H77" s="1">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="I77" s="2">
         <v>6.1</v>
       </c>
       <c r="J77">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K77" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -23717,25 +23717,25 @@
         <v>39</v>
       </c>
       <c r="E78">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F78">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G78" s="1">
-        <v>74.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H78" s="1">
-        <v>25.6</v>
+        <v>15.4</v>
       </c>
       <c r="I78" s="2">
         <v>7.3</v>
       </c>
       <c r="J78">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K78" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -23752,25 +23752,25 @@
         <v>31</v>
       </c>
       <c r="E79">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F79">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G79" s="1">
-        <v>64.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H79" s="1">
-        <v>35.5</v>
+        <v>22.6</v>
       </c>
       <c r="I79" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J79">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K79" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -23799,13 +23799,13 @@
         <v>25</v>
       </c>
       <c r="I80" s="2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J80">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K80" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -23822,25 +23822,25 @@
         <v>38</v>
       </c>
       <c r="E81">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F81">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G81" s="1">
-        <v>92.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="H81" s="1">
-        <v>7.9</v>
+        <v>13.2</v>
       </c>
       <c r="I81" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J81">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K81" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -23857,25 +23857,25 @@
         <v>29</v>
       </c>
       <c r="E82">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F82">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G82" s="1">
-        <v>44.8</v>
+        <v>65.5</v>
       </c>
       <c r="H82" s="1">
-        <v>55.2</v>
+        <v>34.5</v>
       </c>
       <c r="I82" s="2">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="J82">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K82" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -23892,25 +23892,25 @@
         <v>23</v>
       </c>
       <c r="E83">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F83">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G83" s="1">
-        <v>60.9</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H83" s="1">
-        <v>39.1</v>
+        <v>30.4</v>
       </c>
       <c r="I83" s="2">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J83">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K83" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -23942,10 +23942,10 @@
         <v>6.1</v>
       </c>
       <c r="J84">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K84" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -23962,25 +23962,25 @@
         <v>12</v>
       </c>
       <c r="E85">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F85">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G85" s="1">
-        <v>41.7</v>
+        <v>66.7</v>
       </c>
       <c r="H85" s="1">
-        <v>58.3</v>
+        <v>33.3</v>
       </c>
       <c r="I85" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J85">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K85" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -23997,25 +23997,25 @@
         <v>26</v>
       </c>
       <c r="E86">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F86">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G86" s="1">
-        <v>53.8</v>
+        <v>88.5</v>
       </c>
       <c r="H86" s="1">
-        <v>46.2</v>
+        <v>11.5</v>
       </c>
       <c r="I86" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J86">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K86" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -24044,13 +24044,13 @@
         <v>25</v>
       </c>
       <c r="I87" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J87">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K87" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -24067,25 +24067,25 @@
         <v>15</v>
       </c>
       <c r="E88">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G88" s="1">
-        <v>80</v>
+        <v>93.3</v>
       </c>
       <c r="H88" s="1">
-        <v>20</v>
+        <v>6.7</v>
       </c>
       <c r="I88" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J88">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K88" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -24102,25 +24102,25 @@
         <v>25</v>
       </c>
       <c r="E89">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F89">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G89" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H89" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I89" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J89">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K89" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -24134,25 +24134,25 @@
         <v>352</v>
       </c>
       <c r="E90">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="F90">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="G90" s="1">
-        <v>67</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H90" s="1">
-        <v>33</v>
+        <v>22.4</v>
       </c>
       <c r="I90" s="2">
         <v>6.7</v>
       </c>
       <c r="J90">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="K90" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -24169,25 +24169,25 @@
         <v>23</v>
       </c>
       <c r="E91">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F91">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G91" s="1">
-        <v>91.3</v>
+        <v>78.3</v>
       </c>
       <c r="H91" s="1">
-        <v>8.699999999999999</v>
+        <v>21.7</v>
       </c>
       <c r="I91" s="2">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J91">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K91" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -24204,25 +24204,25 @@
         <v>23</v>
       </c>
       <c r="E92">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F92">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G92" s="1">
-        <v>65.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H92" s="1">
-        <v>34.8</v>
+        <v>26.1</v>
       </c>
       <c r="I92" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J92">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K92" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -24239,25 +24239,25 @@
         <v>31</v>
       </c>
       <c r="E93">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F93">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G93" s="1">
-        <v>71</v>
+        <v>64.5</v>
       </c>
       <c r="H93" s="1">
-        <v>29</v>
+        <v>35.5</v>
       </c>
       <c r="I93" s="2">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="J93">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K93" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -24286,13 +24286,13 @@
         <v>21.1</v>
       </c>
       <c r="I94" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J94">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K94" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -24321,13 +24321,13 @@
         <v>4</v>
       </c>
       <c r="I95" s="2">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="J95">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K95" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -24344,25 +24344,25 @@
         <v>30</v>
       </c>
       <c r="E96">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F96">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G96" s="1">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="H96" s="1">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
       <c r="I96" s="2">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="J96">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K96" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -24376,25 +24376,25 @@
         <v>151</v>
       </c>
       <c r="E97">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F97">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G97" s="1">
-        <v>82.8</v>
+        <v>79.5</v>
       </c>
       <c r="H97" s="1">
-        <v>17.2</v>
+        <v>20.5</v>
       </c>
       <c r="I97" s="2">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J97">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="K97" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -24411,25 +24411,25 @@
         <v>30</v>
       </c>
       <c r="E98">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F98">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G98" s="1">
-        <v>83.3</v>
+        <v>93.3</v>
       </c>
       <c r="H98" s="1">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
       <c r="I98" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J98">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K98" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -24446,25 +24446,25 @@
         <v>24</v>
       </c>
       <c r="E99">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F99">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G99" s="1">
-        <v>79.2</v>
+        <v>95.8</v>
       </c>
       <c r="H99" s="1">
-        <v>20.8</v>
+        <v>4.2</v>
       </c>
       <c r="I99" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J99">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K99" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -24481,25 +24481,25 @@
         <v>28</v>
       </c>
       <c r="E100">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F100">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G100" s="1">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H100" s="1">
-        <v>14.3</v>
+        <v>7.1</v>
       </c>
       <c r="I100" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J100">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K100" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -24516,25 +24516,25 @@
         <v>26</v>
       </c>
       <c r="E101">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F101">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G101" s="1">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="H101" s="1">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="I101" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J101">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K101" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -24551,25 +24551,25 @@
         <v>15</v>
       </c>
       <c r="E102">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F102">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G102" s="1">
-        <v>73.3</v>
+        <v>93.3</v>
       </c>
       <c r="H102" s="1">
-        <v>26.7</v>
+        <v>6.7</v>
       </c>
       <c r="I102" s="2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="J102">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K102" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -24583,25 +24583,25 @@
         <v>123</v>
       </c>
       <c r="E103">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="F103">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G103" s="1">
-        <v>81.3</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H103" s="1">
-        <v>18.7</v>
+        <v>4.9</v>
       </c>
       <c r="I103" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J103">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="K103" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -24618,25 +24618,25 @@
         <v>25</v>
       </c>
       <c r="E104">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F104">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G104" s="1">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H104" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I104" s="2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J104">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K104" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -24665,13 +24665,13 @@
         <v>0</v>
       </c>
       <c r="I105" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J105">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K105" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -24703,10 +24703,10 @@
         <v>9.5</v>
       </c>
       <c r="J106">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -24735,13 +24735,13 @@
         <v>0</v>
       </c>
       <c r="I107" s="2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J107">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K107" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -24758,25 +24758,25 @@
         <v>45</v>
       </c>
       <c r="E108">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F108">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G108" s="1">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="H108" s="1">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="I108" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J108">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -24793,25 +24793,25 @@
         <v>31</v>
       </c>
       <c r="E109">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F109">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G109" s="1">
-        <v>87.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="H109" s="1">
-        <v>12.9</v>
+        <v>3.2</v>
       </c>
       <c r="I109" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J109">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K109" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -24840,13 +24840,13 @@
         <v>5.3</v>
       </c>
       <c r="I110" s="2">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J110">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K110" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -24875,13 +24875,13 @@
         <v>5.3</v>
       </c>
       <c r="I111" s="2">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J111">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K111" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -24895,25 +24895,25 @@
         <v>283</v>
       </c>
       <c r="E112">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="F112">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G112" s="1">
-        <v>93.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="H112" s="1">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="I112" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J112">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="K112" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -24930,25 +24930,25 @@
         <v>42</v>
       </c>
       <c r="E113">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G113" s="1">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H113" s="1">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I113" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J113">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K113" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -24965,25 +24965,25 @@
         <v>42</v>
       </c>
       <c r="E114">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G114" s="1">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H114" s="1">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I114" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J114">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K114" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -24997,25 +24997,25 @@
         <v>84</v>
       </c>
       <c r="E115">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F115">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G115" s="1">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H115" s="1">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I115" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J115">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="K115" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -25032,25 +25032,25 @@
         <v>35</v>
       </c>
       <c r="E116">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F116">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G116" s="1">
-        <v>88.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H116" s="1">
-        <v>11.4</v>
+        <v>8.6</v>
       </c>
       <c r="I116" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J116">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K116" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -25067,25 +25067,25 @@
         <v>21</v>
       </c>
       <c r="E117">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F117">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G117" s="1">
-        <v>95.2</v>
+        <v>85.7</v>
       </c>
       <c r="H117" s="1">
-        <v>4.8</v>
+        <v>14.3</v>
       </c>
       <c r="I117" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J117">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K117" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -25099,25 +25099,25 @@
         <v>56</v>
       </c>
       <c r="E118">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F118">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G118" s="1">
-        <v>91.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="H118" s="1">
-        <v>8.9</v>
+        <v>10.7</v>
       </c>
       <c r="I118" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J118">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K118" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -25134,25 +25134,25 @@
         <v>30</v>
       </c>
       <c r="E119">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F119">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G119" s="1">
-        <v>56.7</v>
+        <v>76.7</v>
       </c>
       <c r="H119" s="1">
-        <v>43.3</v>
+        <v>23.3</v>
       </c>
       <c r="I119" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J119">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K119" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -25169,25 +25169,25 @@
         <v>29</v>
       </c>
       <c r="E120">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F120">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G120" s="1">
-        <v>62.1</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H120" s="1">
-        <v>37.9</v>
+        <v>6.9</v>
       </c>
       <c r="I120" s="2">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="J120">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K120" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -25204,25 +25204,25 @@
         <v>23</v>
       </c>
       <c r="E121">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F121">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G121" s="1">
-        <v>78.3</v>
+        <v>87</v>
       </c>
       <c r="H121" s="1">
-        <v>21.7</v>
+        <v>13</v>
       </c>
       <c r="I121" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J121">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K121" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -25239,25 +25239,25 @@
         <v>33</v>
       </c>
       <c r="E122">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F122">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G122" s="1">
-        <v>66.7</v>
+        <v>81.8</v>
       </c>
       <c r="H122" s="1">
-        <v>33.3</v>
+        <v>18.2</v>
       </c>
       <c r="I122" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J122">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K122" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -25271,28 +25271,28 @@
         <v>133</v>
       </c>
       <c r="D123">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E123">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F123">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G123" s="1">
-        <v>71.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="H123" s="1">
-        <v>28.6</v>
+        <v>13.3</v>
       </c>
       <c r="I123" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J123">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K123" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -25303,28 +25303,28 @@
         <v>121</v>
       </c>
       <c r="D124">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E124">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="F124">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="G124" s="1">
-        <v>65.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H124" s="1">
-        <v>34.1</v>
+        <v>15.4</v>
       </c>
       <c r="I124" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J124">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="K124" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -25341,25 +25341,25 @@
         <v>31</v>
       </c>
       <c r="E125">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F125">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G125" s="1">
-        <v>77.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H125" s="1">
-        <v>22.6</v>
+        <v>0</v>
       </c>
       <c r="I125" s="2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="J125">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K125" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -25376,25 +25376,25 @@
         <v>35</v>
       </c>
       <c r="E126">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F126">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G126" s="1">
-        <v>68.59999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H126" s="1">
-        <v>31.4</v>
+        <v>11.4</v>
       </c>
       <c r="I126" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J126">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -25411,25 +25411,25 @@
         <v>35</v>
       </c>
       <c r="E127">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F127">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G127" s="1">
-        <v>85.7</v>
+        <v>94.3</v>
       </c>
       <c r="H127" s="1">
-        <v>14.3</v>
+        <v>5.7</v>
       </c>
       <c r="I127" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J127">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K127" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -25446,25 +25446,25 @@
         <v>24</v>
       </c>
       <c r="E128">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G128" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H128" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I128" s="2">
         <v>8</v>
       </c>
       <c r="J128">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K128" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -25478,25 +25478,25 @@
         <v>125</v>
       </c>
       <c r="E129">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="F129">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G129" s="1">
-        <v>80</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H129" s="1">
-        <v>20</v>
+        <v>5.6</v>
       </c>
       <c r="I129" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J129">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="K129" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -25583,25 +25583,25 @@
         <v>30</v>
       </c>
       <c r="E132">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F132">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G132" s="1">
-        <v>76.7</v>
+        <v>90</v>
       </c>
       <c r="H132" s="1">
-        <v>23.3</v>
+        <v>10</v>
       </c>
       <c r="I132" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J132">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K132" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -25633,10 +25633,10 @@
         <v>9</v>
       </c>
       <c r="J133">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K133" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -25653,25 +25653,25 @@
         <v>26</v>
       </c>
       <c r="E134">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F134">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G134" s="1">
-        <v>73.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H134" s="1">
-        <v>26.9</v>
+        <v>0</v>
       </c>
       <c r="I134" s="2">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="J134">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K134" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -25685,28 +25685,28 @@
         <v>133</v>
       </c>
       <c r="D135">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E135">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F135">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G135" s="1">
-        <v>64.3</v>
+        <v>73.3</v>
       </c>
       <c r="H135" s="1">
-        <v>35.7</v>
+        <v>26.7</v>
       </c>
       <c r="I135" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J135">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K135" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -25717,28 +25717,28 @@
         <v>121</v>
       </c>
       <c r="D136">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E136">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="F136">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G136" s="1">
-        <v>84.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="H136" s="1">
-        <v>15.6</v>
+        <v>7.7</v>
       </c>
       <c r="I136" s="2">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J136">
-        <v>154</v>
+        <v>60</v>
       </c>
       <c r="K136" s="1">
-        <v>100</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -25767,13 +25767,13 @@
         <v>0</v>
       </c>
       <c r="I137" s="2">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="J137">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K137" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -25790,25 +25790,25 @@
         <v>30</v>
       </c>
       <c r="E138">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138" s="1">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H138" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I138" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J138">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K138" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -25825,25 +25825,25 @@
         <v>30</v>
       </c>
       <c r="E139">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G139" s="1">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H139" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I139" s="2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J139">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -25872,13 +25872,13 @@
         <v>3.6</v>
       </c>
       <c r="I140" s="2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J140">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K140" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -25907,13 +25907,13 @@
         <v>3.6</v>
       </c>
       <c r="I141" s="2">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J141">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K141" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -25927,25 +25927,25 @@
         <v>146</v>
       </c>
       <c r="E142">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F142">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G142" s="1">
-        <v>97.3</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H142" s="1">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="I142" s="2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J142">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="K142" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -26029,25 +26029,25 @@
         <v>32</v>
       </c>
       <c r="E145">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F145">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G145" s="1">
-        <v>78.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H145" s="1">
-        <v>21.9</v>
+        <v>0</v>
       </c>
       <c r="I145" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J145">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K145" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -26061,25 +26061,25 @@
         <v>32</v>
       </c>
       <c r="E146">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F146">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G146" s="1">
-        <v>78.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H146" s="1">
-        <v>21.9</v>
+        <v>0</v>
       </c>
       <c r="I146" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J146">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K146" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -26108,13 +26108,13 @@
         <v>4</v>
       </c>
       <c r="I147" s="2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J147">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K147" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -26131,25 +26131,25 @@
         <v>26</v>
       </c>
       <c r="E148">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F148">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G148" s="1">
-        <v>92.3</v>
+        <v>88.5</v>
       </c>
       <c r="H148" s="1">
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="I148" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="J148">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K148" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -26163,25 +26163,25 @@
         <v>51</v>
       </c>
       <c r="E149">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F149">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G149" s="1">
-        <v>94.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="H149" s="1">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="I149" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J149">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K149" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -26195,10 +26195,10 @@
         <v>131</v>
       </c>
       <c r="D150">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E150">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -26213,10 +26213,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J150">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -26227,10 +26227,10 @@
         <v>121</v>
       </c>
       <c r="D151">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E151">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -26245,10 +26245,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J151">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -26265,25 +26265,25 @@
         <v>35</v>
       </c>
       <c r="E152">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F152">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G152" s="1">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H152" s="1">
-        <v>20</v>
+        <v>11.4</v>
       </c>
       <c r="I152" s="2">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J152">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -26300,25 +26300,25 @@
         <v>34</v>
       </c>
       <c r="E153">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F153">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G153" s="1">
-        <v>79.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="H153" s="1">
-        <v>20.6</v>
+        <v>11.8</v>
       </c>
       <c r="I153" s="2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J153">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K153" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -26335,25 +26335,25 @@
         <v>45</v>
       </c>
       <c r="E154">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F154">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G154" s="1">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="H154" s="1">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="I154" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J154">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K154" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -26367,25 +26367,25 @@
         <v>114</v>
       </c>
       <c r="E155">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F155">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G155" s="1">
-        <v>86</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H155" s="1">
-        <v>14</v>
+        <v>7.9</v>
       </c>
       <c r="I155" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J155">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="K155" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -26446,10 +26446,10 @@
         <v>0</v>
       </c>
       <c r="J157">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="K157" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -26475,10 +26475,10 @@
         <v>0</v>
       </c>
       <c r="J158">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="K158" s="1">
-        <v>100</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -26495,25 +26495,25 @@
         <v>25</v>
       </c>
       <c r="E159">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F159">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G159" s="1">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H159" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I159" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J159">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K159" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -26545,10 +26545,10 @@
         <v>8.5</v>
       </c>
       <c r="J160">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K160" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -26565,25 +26565,25 @@
         <v>31</v>
       </c>
       <c r="E161">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F161">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G161" s="1">
-        <v>83.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H161" s="1">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="I161" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J161">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K161" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -26600,25 +26600,25 @@
         <v>35</v>
       </c>
       <c r="E162">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F162">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G162" s="1">
-        <v>85.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H162" s="1">
-        <v>14.3</v>
+        <v>11.4</v>
       </c>
       <c r="I162" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J162">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K162" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -26635,25 +26635,25 @@
         <v>24</v>
       </c>
       <c r="E163">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F163">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G163" s="1">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="H163" s="1">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="I163" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J163">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K163" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -26685,10 +26685,10 @@
         <v>9</v>
       </c>
       <c r="J164">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K164" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -26702,25 +26702,25 @@
         <v>192</v>
       </c>
       <c r="E165">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="F165">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G165" s="1">
-        <v>85.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H165" s="1">
-        <v>14.6</v>
+        <v>9.4</v>
       </c>
       <c r="I165" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J165">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="K165" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -26737,25 +26737,25 @@
         <v>31</v>
       </c>
       <c r="E166">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F166">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G166" s="1">
-        <v>54.8</v>
+        <v>90.3</v>
       </c>
       <c r="H166" s="1">
-        <v>45.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I166" s="2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J166">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K166" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -26772,25 +26772,25 @@
         <v>21</v>
       </c>
       <c r="E167">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F167">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G167" s="1">
-        <v>76.2</v>
+        <v>85.7</v>
       </c>
       <c r="H167" s="1">
-        <v>23.8</v>
+        <v>14.3</v>
       </c>
       <c r="I167" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J167">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K167" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -26819,13 +26819,13 @@
         <v>4</v>
       </c>
       <c r="I168" s="2">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J168">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K168" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -26842,25 +26842,25 @@
         <v>30</v>
       </c>
       <c r="E169">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F169">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G169" s="1">
-        <v>80</v>
+        <v>93.3</v>
       </c>
       <c r="H169" s="1">
-        <v>20</v>
+        <v>6.7</v>
       </c>
       <c r="I169" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J169">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K169" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -26874,25 +26874,25 @@
         <v>107</v>
       </c>
       <c r="E170">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F170">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G170" s="1">
-        <v>75.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H170" s="1">
-        <v>24.3</v>
+        <v>8.4</v>
       </c>
       <c r="I170" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J170">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="K170" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -26909,25 +26909,25 @@
         <v>30</v>
       </c>
       <c r="E171">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F171">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G171" s="1">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H171" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I171" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J171">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K171" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -26956,13 +26956,13 @@
         <v>0</v>
       </c>
       <c r="I172" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J172">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K172" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -26979,25 +26979,25 @@
         <v>24</v>
       </c>
       <c r="E173">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F173">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G173" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H173" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I173" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J173">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K173" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -27011,10 +27011,10 @@
         <v>131</v>
       </c>
       <c r="D174">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E174">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F174">
         <v>0</v>
@@ -27026,13 +27026,13 @@
         <v>0</v>
       </c>
       <c r="I174" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J174">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K174" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -27049,25 +27049,25 @@
         <v>28</v>
       </c>
       <c r="E175">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F175">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G175" s="1">
-        <v>75</v>
+        <v>85.7</v>
       </c>
       <c r="H175" s="1">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="I175" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J175">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K175" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -27084,25 +27084,25 @@
         <v>37</v>
       </c>
       <c r="E176">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F176">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G176" s="1">
-        <v>86.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H176" s="1">
-        <v>13.5</v>
+        <v>5.4</v>
       </c>
       <c r="I176" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J176">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K176" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -27113,28 +27113,28 @@
         <v>121</v>
       </c>
       <c r="D177">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E177">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="F177">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G177" s="1">
-        <v>87.7</v>
+        <v>94.7</v>
       </c>
       <c r="H177" s="1">
-        <v>12.3</v>
+        <v>5.3</v>
       </c>
       <c r="I177" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J177">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="K177" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -27151,25 +27151,25 @@
         <v>25</v>
       </c>
       <c r="E178">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F178">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G178" s="1">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="H178" s="1">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="I178" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J178">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K178" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -27186,25 +27186,25 @@
         <v>39</v>
       </c>
       <c r="E179">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F179">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G179" s="1">
-        <v>89.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H179" s="1">
-        <v>10.3</v>
+        <v>5.1</v>
       </c>
       <c r="I179" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J179">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K179" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -27221,25 +27221,25 @@
         <v>24</v>
       </c>
       <c r="E180">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F180">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G180" s="1">
-        <v>75</v>
+        <v>95.8</v>
       </c>
       <c r="H180" s="1">
-        <v>25</v>
+        <v>4.2</v>
       </c>
       <c r="I180" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J180">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K180" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -27256,25 +27256,25 @@
         <v>38</v>
       </c>
       <c r="E181">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F181">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G181" s="1">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H181" s="1">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="I181" s="2">
         <v>8.4</v>
       </c>
       <c r="J181">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K181" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -27291,25 +27291,25 @@
         <v>30</v>
       </c>
       <c r="E182">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F182">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G182" s="1">
-        <v>80</v>
+        <v>96.7</v>
       </c>
       <c r="H182" s="1">
-        <v>20</v>
+        <v>3.3</v>
       </c>
       <c r="I182" s="2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J182">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K182" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -27326,25 +27326,25 @@
         <v>29</v>
       </c>
       <c r="E183">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F183">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G183" s="1">
-        <v>79.3</v>
+        <v>100</v>
       </c>
       <c r="H183" s="1">
-        <v>20.7</v>
+        <v>0</v>
       </c>
       <c r="I183" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J183">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K183" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -27361,25 +27361,25 @@
         <v>23</v>
       </c>
       <c r="E184">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G184" s="1">
-        <v>91.3</v>
+        <v>95.7</v>
       </c>
       <c r="H184" s="1">
-        <v>8.699999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="I184" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J184">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K184" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -27396,25 +27396,25 @@
         <v>33</v>
       </c>
       <c r="E185">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F185">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G185" s="1">
-        <v>84.8</v>
+        <v>100</v>
       </c>
       <c r="H185" s="1">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="I185" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J185">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K185" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -27431,25 +27431,25 @@
         <v>12</v>
       </c>
       <c r="E186">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F186">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G186" s="1">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="H186" s="1">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="I186" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J186">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K186" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -27481,10 +27481,10 @@
         <v>8.5</v>
       </c>
       <c r="J187">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -27498,28 +27498,28 @@
         <v>133</v>
       </c>
       <c r="D188">
+        <v>15</v>
+      </c>
+      <c r="E188">
         <v>14</v>
-      </c>
-      <c r="E188">
-        <v>13</v>
       </c>
       <c r="F188">
         <v>1</v>
       </c>
       <c r="G188" s="1">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="H188" s="1">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I188" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J188">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K188" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -27530,28 +27530,28 @@
         <v>121</v>
       </c>
       <c r="D189">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E189">
-        <v>233</v>
+        <v>273</v>
       </c>
       <c r="F189">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="G189" s="1">
-        <v>82.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="H189" s="1">
-        <v>17.4</v>
+        <v>3.5</v>
       </c>
       <c r="I189" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J189">
-        <v>282</v>
+        <v>0</v>
       </c>
       <c r="K189" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -27568,25 +27568,25 @@
         <v>31</v>
       </c>
       <c r="E190">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F190">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G190" s="1">
-        <v>87.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H190" s="1">
-        <v>12.9</v>
+        <v>16.1</v>
       </c>
       <c r="I190" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J190">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K190" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -27615,13 +27615,13 @@
         <v>3.1</v>
       </c>
       <c r="I191" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J191">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K191" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -27635,25 +27635,25 @@
         <v>63</v>
       </c>
       <c r="E192">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F192">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G192" s="1">
-        <v>92.09999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="H192" s="1">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="I192" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J192">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="K192" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -27670,25 +27670,25 @@
         <v>29</v>
       </c>
       <c r="E193">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F193">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G193" s="1">
-        <v>89.7</v>
+        <v>82.8</v>
       </c>
       <c r="H193" s="1">
-        <v>10.3</v>
+        <v>17.2</v>
       </c>
       <c r="I193" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J193">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K193" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -27705,25 +27705,25 @@
         <v>42</v>
       </c>
       <c r="E194">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F194">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G194" s="1">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="H194" s="1">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="I194" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J194">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K194" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -27740,25 +27740,25 @@
         <v>35</v>
       </c>
       <c r="E195">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F195">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G195" s="1">
-        <v>91.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="H195" s="1">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="I195" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J195">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K195" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -27775,25 +27775,25 @@
         <v>45</v>
       </c>
       <c r="E196">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F196">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G196" s="1">
-        <v>95.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="H196" s="1">
-        <v>4.4</v>
+        <v>17.8</v>
       </c>
       <c r="I196" s="2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J196">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K196" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:11">
@@ -27810,25 +27810,25 @@
         <v>31</v>
       </c>
       <c r="E197">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F197">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G197" s="1">
-        <v>96.8</v>
+        <v>90.3</v>
       </c>
       <c r="H197" s="1">
-        <v>3.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I197" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J197">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K197" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -27857,13 +27857,13 @@
         <v>5.3</v>
       </c>
       <c r="I198" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J198">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K198" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -27895,10 +27895,10 @@
         <v>9.1</v>
       </c>
       <c r="J199">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K199" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -27915,25 +27915,25 @@
         <v>37</v>
       </c>
       <c r="E200">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F200">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G200" s="1">
-        <v>91.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H200" s="1">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="I200" s="2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J200">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K200" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -27947,25 +27947,25 @@
         <v>294</v>
       </c>
       <c r="E201">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="F201">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G201" s="1">
-        <v>94.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="H201" s="1">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
       <c r="I201" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J201">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="K201" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:11">
@@ -27994,7 +27994,7 @@
         <v>6.9</v>
       </c>
       <c r="I202" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J202">
         <v>29</v>
@@ -28096,7 +28096,7 @@
         <v>19.4</v>
       </c>
       <c r="I205" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J205">
         <v>31</v>
@@ -28128,7 +28128,7 @@
         <v>16.5</v>
       </c>
       <c r="I206" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J206">
         <v>103</v>
@@ -28151,25 +28151,25 @@
         <v>31</v>
       </c>
       <c r="E207">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F207">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G207" s="1">
-        <v>80.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="H207" s="1">
-        <v>19.4</v>
+        <v>6.5</v>
       </c>
       <c r="I207" s="2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="J207">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K207" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -28198,13 +28198,13 @@
         <v>25</v>
       </c>
       <c r="I208" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J208">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K208" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -28221,25 +28221,25 @@
         <v>35</v>
       </c>
       <c r="E209">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F209">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G209" s="1">
-        <v>80</v>
+        <v>94.3</v>
       </c>
       <c r="H209" s="1">
-        <v>20</v>
+        <v>5.7</v>
       </c>
       <c r="I209" s="2">
         <v>7.7</v>
       </c>
       <c r="J209">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K209" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -28268,13 +28268,13 @@
         <v>4.2</v>
       </c>
       <c r="I210" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J210">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K210" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:11">
@@ -28288,25 +28288,25 @@
         <v>102</v>
       </c>
       <c r="E211">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F211">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G211" s="1">
-        <v>83.3</v>
+        <v>92.2</v>
       </c>
       <c r="H211" s="1">
-        <v>16.7</v>
+        <v>7.8</v>
       </c>
       <c r="I211" s="2">
         <v>7.8</v>
       </c>
       <c r="J211">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="K211" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:11">
@@ -28323,25 +28323,25 @@
         <v>30</v>
       </c>
       <c r="E212">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F212">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G212" s="1">
-        <v>43.3</v>
+        <v>46.7</v>
       </c>
       <c r="H212" s="1">
-        <v>56.7</v>
+        <v>53.3</v>
       </c>
       <c r="I212" s="2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J212">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K212" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:11">
@@ -28358,25 +28358,25 @@
         <v>29</v>
       </c>
       <c r="E213">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F213">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G213" s="1">
-        <v>48.3</v>
+        <v>44.8</v>
       </c>
       <c r="H213" s="1">
-        <v>51.7</v>
+        <v>55.2</v>
       </c>
       <c r="I213" s="2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J213">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K213" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:11">
@@ -28408,10 +28408,10 @@
         <v>5.7</v>
       </c>
       <c r="J214">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K214" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:11">
@@ -28428,25 +28428,25 @@
         <v>12</v>
       </c>
       <c r="E215">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F215">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G215" s="1">
-        <v>58.3</v>
+        <v>75</v>
       </c>
       <c r="H215" s="1">
-        <v>41.7</v>
+        <v>25</v>
       </c>
       <c r="I215" s="2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J215">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K215" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -28475,13 +28475,13 @@
         <v>13.3</v>
       </c>
       <c r="I216" s="2">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="J216">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K216" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -28495,25 +28495,25 @@
         <v>109</v>
       </c>
       <c r="E217">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F217">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G217" s="1">
-        <v>56</v>
+        <v>57.8</v>
       </c>
       <c r="H217" s="1">
-        <v>44</v>
+        <v>42.2</v>
       </c>
       <c r="I217" s="2">
         <v>5.9</v>
       </c>
       <c r="J217">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="K217" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:11">
@@ -28530,25 +28530,25 @@
         <v>25</v>
       </c>
       <c r="E218">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F218">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G218" s="1">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H218" s="1">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I218" s="2">
         <v>6.9</v>
       </c>
       <c r="J218">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K218" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:11">
@@ -28565,25 +28565,25 @@
         <v>39</v>
       </c>
       <c r="E219">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F219">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G219" s="1">
-        <v>89.7</v>
+        <v>92.3</v>
       </c>
       <c r="H219" s="1">
-        <v>10.3</v>
+        <v>7.7</v>
       </c>
       <c r="I219" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J219">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K219" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:11">
@@ -28612,13 +28612,13 @@
         <v>11.4</v>
       </c>
       <c r="I220" s="2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J220">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K220" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:11">
@@ -28635,25 +28635,25 @@
         <v>24</v>
       </c>
       <c r="E221">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F221">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G221" s="1">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="H221" s="1">
-        <v>12.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I221" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J221">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K221" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:11">
@@ -28685,10 +28685,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J222">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K222" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:11">
@@ -28705,25 +28705,25 @@
         <v>34</v>
       </c>
       <c r="E223">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F223">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G223" s="1">
-        <v>73.5</v>
+        <v>88.2</v>
       </c>
       <c r="H223" s="1">
-        <v>26.5</v>
+        <v>11.8</v>
       </c>
       <c r="I223" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J223">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K223" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:11">
@@ -28740,25 +28740,25 @@
         <v>25</v>
       </c>
       <c r="E224">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F224">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G224" s="1">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H224" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I224" s="2">
         <v>8.5</v>
       </c>
       <c r="J224">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K224" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:11">
@@ -28772,25 +28772,25 @@
         <v>220</v>
       </c>
       <c r="E225">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="F225">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G225" s="1">
-        <v>85.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H225" s="1">
-        <v>14.5</v>
+        <v>8.6</v>
       </c>
       <c r="I225" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J225">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="K225" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:11">
@@ -28807,25 +28807,25 @@
         <v>30</v>
       </c>
       <c r="E226">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F226">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G226" s="1">
-        <v>76.7</v>
+        <v>83.3</v>
       </c>
       <c r="H226" s="1">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="I226" s="2">
         <v>7</v>
       </c>
       <c r="J226">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K226" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -28842,25 +28842,25 @@
         <v>23</v>
       </c>
       <c r="E227">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F227">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G227" s="1">
-        <v>87</v>
+        <v>95.7</v>
       </c>
       <c r="H227" s="1">
-        <v>13</v>
+        <v>4.3</v>
       </c>
       <c r="I227" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J227">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K227" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228" spans="1:11">
@@ -28889,13 +28889,13 @@
         <v>4.3</v>
       </c>
       <c r="I228" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="J228">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K228" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:11">
@@ -28912,25 +28912,25 @@
         <v>20</v>
       </c>
       <c r="E229">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G229" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H229" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I229" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J229">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K229" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -28959,13 +28959,13 @@
         <v>4</v>
       </c>
       <c r="I230" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J230">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K230" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -28982,25 +28982,25 @@
         <v>30</v>
       </c>
       <c r="E231">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F231">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G231" s="1">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="H231" s="1">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="I231" s="2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="J231">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K231" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -29014,25 +29014,25 @@
         <v>151</v>
       </c>
       <c r="E232">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F232">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G232" s="1">
-        <v>89.40000000000001</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H232" s="1">
-        <v>10.6</v>
+        <v>6.6</v>
       </c>
       <c r="I232" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J232">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="K232" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -29049,25 +29049,25 @@
         <v>39</v>
       </c>
       <c r="E233">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F233">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G233" s="1">
-        <v>76.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="H233" s="1">
-        <v>23.1</v>
+        <v>20.5</v>
       </c>
       <c r="I233" s="2">
         <v>6.7</v>
       </c>
       <c r="J233">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K233" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -29084,25 +29084,25 @@
         <v>31</v>
       </c>
       <c r="E234">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F234">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G234" s="1">
-        <v>83.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="H234" s="1">
-        <v>16.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I234" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J234">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K234" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:11">
@@ -29119,25 +29119,25 @@
         <v>35</v>
       </c>
       <c r="E235">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F235">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G235" s="1">
-        <v>68.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H235" s="1">
-        <v>31.4</v>
+        <v>14.3</v>
       </c>
       <c r="I235" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J235">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K235" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -29154,25 +29154,25 @@
         <v>24</v>
       </c>
       <c r="E236">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F236">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G236" s="1">
-        <v>79.2</v>
+        <v>95.8</v>
       </c>
       <c r="H236" s="1">
-        <v>20.8</v>
+        <v>4.2</v>
       </c>
       <c r="I236" s="2">
         <v>6.9</v>
       </c>
       <c r="J236">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K236" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -29189,25 +29189,25 @@
         <v>38</v>
       </c>
       <c r="E237">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F237">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G237" s="1">
-        <v>76.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H237" s="1">
-        <v>23.7</v>
+        <v>18.4</v>
       </c>
       <c r="I237" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J237">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K237" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238" spans="1:11">
@@ -29224,25 +29224,25 @@
         <v>29</v>
       </c>
       <c r="E238">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F238">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G238" s="1">
-        <v>55.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H238" s="1">
-        <v>44.8</v>
+        <v>3.4</v>
       </c>
       <c r="I238" s="2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J238">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K238" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -29259,25 +29259,25 @@
         <v>35</v>
       </c>
       <c r="E239">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F239">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G239" s="1">
-        <v>77.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H239" s="1">
-        <v>22.9</v>
+        <v>14.3</v>
       </c>
       <c r="I239" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J239">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K239" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -29309,10 +29309,10 @@
         <v>6.8</v>
       </c>
       <c r="J240">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K240" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -29329,25 +29329,25 @@
         <v>31</v>
       </c>
       <c r="E241">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F241">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G241" s="1">
-        <v>67.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H241" s="1">
-        <v>32.3</v>
+        <v>12.9</v>
       </c>
       <c r="I241" s="2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J241">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K241" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242" spans="1:11">
@@ -29361,25 +29361,25 @@
         <v>307</v>
       </c>
       <c r="E242">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="F242">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="G242" s="1">
-        <v>72.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H242" s="1">
-        <v>27.4</v>
+        <v>15.6</v>
       </c>
       <c r="I242" s="2">
         <v>6.8</v>
       </c>
       <c r="J242">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="K242" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243" spans="1:11">
@@ -29396,25 +29396,25 @@
         <v>28</v>
       </c>
       <c r="E243">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F243">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G243" s="1">
-        <v>57.1</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H243" s="1">
-        <v>42.9</v>
+        <v>21.4</v>
       </c>
       <c r="I243" s="2">
         <v>6.7</v>
       </c>
       <c r="J243">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K243" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -29428,25 +29428,25 @@
         <v>28</v>
       </c>
       <c r="E244">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F244">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G244" s="1">
-        <v>57.1</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H244" s="1">
-        <v>42.9</v>
+        <v>21.4</v>
       </c>
       <c r="I244" s="2">
         <v>6.7</v>
       </c>
       <c r="J244">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K244" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -29478,10 +29478,10 @@
         <v>7.7</v>
       </c>
       <c r="J245">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K245" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246" spans="1:11">
@@ -29510,10 +29510,10 @@
         <v>7.7</v>
       </c>
       <c r="J246">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K246" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -29530,25 +29530,25 @@
         <v>23</v>
       </c>
       <c r="E247">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F247">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G247" s="1">
-        <v>56.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H247" s="1">
-        <v>43.5</v>
+        <v>30.4</v>
       </c>
       <c r="I247" s="2">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="J247">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K247" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -29565,25 +29565,25 @@
         <v>26</v>
       </c>
       <c r="E248">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F248">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G248" s="1">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="H248" s="1">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="I248" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J248">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K248" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -29612,13 +29612,13 @@
         <v>0</v>
       </c>
       <c r="I249" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J249">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K249" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -29632,25 +29632,25 @@
         <v>75</v>
       </c>
       <c r="E250">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F250">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G250" s="1">
-        <v>85.3</v>
+        <v>90.7</v>
       </c>
       <c r="H250" s="1">
-        <v>14.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I250" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J250">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K250" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -29667,25 +29667,25 @@
         <v>23</v>
       </c>
       <c r="E251">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F251">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G251" s="1">
-        <v>91.3</v>
+        <v>95.7</v>
       </c>
       <c r="H251" s="1">
-        <v>8.699999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="I251" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J251">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K251" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -29714,13 +29714,13 @@
         <v>4.3</v>
       </c>
       <c r="I252" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J252">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K252" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -29737,25 +29737,25 @@
         <v>21</v>
       </c>
       <c r="E253">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F253">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G253" s="1">
-        <v>76.2</v>
+        <v>90.5</v>
       </c>
       <c r="H253" s="1">
-        <v>23.8</v>
+        <v>9.5</v>
       </c>
       <c r="I253" s="2">
         <v>7.3</v>
       </c>
       <c r="J253">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K253" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:11">
@@ -29769,25 +29769,25 @@
         <v>67</v>
       </c>
       <c r="E254">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F254">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G254" s="1">
-        <v>88.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="H254" s="1">
-        <v>11.9</v>
+        <v>6</v>
       </c>
       <c r="I254" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J254">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="K254" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -29804,25 +29804,25 @@
         <v>23</v>
       </c>
       <c r="E255">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F255">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G255" s="1">
-        <v>87</v>
+        <v>91.3</v>
       </c>
       <c r="H255" s="1">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I255" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J255">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K255" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -29839,25 +29839,25 @@
         <v>31</v>
       </c>
       <c r="E256">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F256">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G256" s="1">
-        <v>80.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="H256" s="1">
-        <v>19.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I256" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J256">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K256" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -29874,25 +29874,25 @@
         <v>20</v>
       </c>
       <c r="E257">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F257">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G257" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H257" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I257" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J257">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K257" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -29921,13 +29921,13 @@
         <v>4</v>
       </c>
       <c r="I258" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J258">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K258" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:11">
@@ -29956,13 +29956,13 @@
         <v>0</v>
       </c>
       <c r="I259" s="2">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="J259">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K259" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -29976,25 +29976,25 @@
         <v>129</v>
       </c>
       <c r="E260">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F260">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G260" s="1">
-        <v>89.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="H260" s="1">
-        <v>10.9</v>
+        <v>6.2</v>
       </c>
       <c r="I260" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J260">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="K260" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:11">
@@ -30011,25 +30011,25 @@
         <v>31</v>
       </c>
       <c r="E261">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F261">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G261" s="1">
-        <v>71</v>
+        <v>74.2</v>
       </c>
       <c r="H261" s="1">
-        <v>29</v>
+        <v>25.8</v>
       </c>
       <c r="I261" s="2">
         <v>6.8</v>
       </c>
       <c r="J261">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K261" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -30043,25 +30043,25 @@
         <v>31</v>
       </c>
       <c r="E262">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F262">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G262" s="1">
-        <v>71</v>
+        <v>74.2</v>
       </c>
       <c r="H262" s="1">
-        <v>29</v>
+        <v>25.8</v>
       </c>
       <c r="I262" s="2">
         <v>6.8</v>
       </c>
       <c r="J262">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K262" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:11">
@@ -30090,10 +30090,10 @@
         <v>0</v>
       </c>
       <c r="J263">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K263" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:11">
@@ -30122,10 +30122,10 @@
         <v>0</v>
       </c>
       <c r="J264">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K264" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265" spans="1:11">
@@ -30154,10 +30154,10 @@
         <v>0</v>
       </c>
       <c r="J265">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K265" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266" spans="1:11">
@@ -30186,10 +30186,10 @@
         <v>0</v>
       </c>
       <c r="J266">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K266" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:11">
@@ -30218,10 +30218,10 @@
         <v>0</v>
       </c>
       <c r="J267">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K267" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268" spans="1:11">
@@ -30250,10 +30250,10 @@
         <v>0</v>
       </c>
       <c r="J268">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K268" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269" spans="1:11">
@@ -30279,10 +30279,10 @@
         <v>0</v>
       </c>
       <c r="J269">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="K269" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:11">
@@ -30299,25 +30299,25 @@
         <v>30</v>
       </c>
       <c r="E270">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F270">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G270" s="1">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H270" s="1">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I270" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J270">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K270" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271" spans="1:11">
@@ -30349,10 +30349,10 @@
         <v>8.9</v>
       </c>
       <c r="J271">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K271" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272" spans="1:11">
@@ -30369,25 +30369,25 @@
         <v>24</v>
       </c>
       <c r="E272">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F272">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G272" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H272" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I272" s="2">
         <v>8.4</v>
       </c>
       <c r="J272">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K272" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273" spans="1:11">
@@ -30401,10 +30401,10 @@
         <v>131</v>
       </c>
       <c r="D273">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E273">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F273">
         <v>0</v>
@@ -30419,10 +30419,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J273">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K273" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274" spans="1:11">
@@ -30439,25 +30439,25 @@
         <v>28</v>
       </c>
       <c r="E274">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F274">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G274" s="1">
-        <v>75</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H274" s="1">
-        <v>25</v>
+        <v>3.6</v>
       </c>
       <c r="I274" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J274">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K274" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275" spans="1:11">
@@ -30474,25 +30474,25 @@
         <v>37</v>
       </c>
       <c r="E275">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F275">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G275" s="1">
-        <v>91.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H275" s="1">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="I275" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J275">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K275" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276" spans="1:11">
@@ -30503,28 +30503,28 @@
         <v>121</v>
       </c>
       <c r="D276">
+        <v>189</v>
+      </c>
+      <c r="E276">
         <v>187</v>
       </c>
-      <c r="E276">
-        <v>170</v>
-      </c>
       <c r="F276">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G276" s="1">
-        <v>90.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H276" s="1">
-        <v>9.1</v>
+        <v>1.1</v>
       </c>
       <c r="I276" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J276">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="K276" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277" spans="1:11">
@@ -30541,25 +30541,25 @@
         <v>30</v>
       </c>
       <c r="E277">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F277">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G277" s="1">
-        <v>36.7</v>
+        <v>76.7</v>
       </c>
       <c r="H277" s="1">
-        <v>63.3</v>
+        <v>23.3</v>
       </c>
       <c r="I277" s="2">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="J277">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K277" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278" spans="1:11">
@@ -30576,25 +30576,25 @@
         <v>29</v>
       </c>
       <c r="E278">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="F278">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G278" s="1">
-        <v>20.7</v>
+        <v>100</v>
       </c>
       <c r="H278" s="1">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="I278" s="2">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="J278">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K278" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279" spans="1:11">
@@ -30611,25 +30611,25 @@
         <v>33</v>
       </c>
       <c r="E279">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F279">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G279" s="1">
-        <v>54.5</v>
+        <v>78.8</v>
       </c>
       <c r="H279" s="1">
-        <v>45.5</v>
+        <v>21.2</v>
       </c>
       <c r="I279" s="2">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="J279">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K279" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280" spans="1:11">
@@ -30646,25 +30646,25 @@
         <v>33</v>
       </c>
       <c r="E280">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F280">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G280" s="1">
-        <v>39.4</v>
+        <v>78.8</v>
       </c>
       <c r="H280" s="1">
-        <v>60.6</v>
+        <v>21.2</v>
       </c>
       <c r="I280" s="2">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J280">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K280" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:11">
@@ -30681,25 +30681,25 @@
         <v>12</v>
       </c>
       <c r="E281">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F281">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G281" s="1">
-        <v>41.7</v>
+        <v>75</v>
       </c>
       <c r="H281" s="1">
-        <v>58.3</v>
+        <v>25</v>
       </c>
       <c r="I281" s="2">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="J281">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K281" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282" spans="1:11">
@@ -30713,25 +30713,25 @@
         <v>137</v>
       </c>
       <c r="E282">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="F282">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="G282" s="1">
-        <v>38.7</v>
+        <v>82.5</v>
       </c>
       <c r="H282" s="1">
-        <v>61.3</v>
+        <v>17.5</v>
       </c>
       <c r="I282" s="2">
-        <v>5.9</v>
+        <v>6.7</v>
       </c>
       <c r="J282">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="K282" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283" spans="1:11">
@@ -30760,13 +30760,13 @@
         <v>0</v>
       </c>
       <c r="I283" s="2">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J283">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K283" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284" spans="1:11">
@@ -30783,25 +30783,25 @@
         <v>24</v>
       </c>
       <c r="E284">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F284">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G284" s="1">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H284" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I284" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J284">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K284" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:11">
@@ -30818,25 +30818,25 @@
         <v>30</v>
       </c>
       <c r="E285">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F285">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G285" s="1">
-        <v>76.7</v>
+        <v>83.3</v>
       </c>
       <c r="H285" s="1">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="I285" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J285">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K285" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286" spans="1:11">
@@ -30853,25 +30853,25 @@
         <v>23</v>
       </c>
       <c r="E286">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G286" s="1">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="H286" s="1">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="I286" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J286">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K286" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287" spans="1:11">
@@ -30885,25 +30885,25 @@
         <v>108</v>
       </c>
       <c r="E287">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F287">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G287" s="1">
-        <v>89.8</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="H287" s="1">
-        <v>10.2</v>
+        <v>4.6</v>
       </c>
       <c r="I287" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J287">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="K287" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288" spans="1:11">
@@ -30932,13 +30932,13 @@
         <v>2.4</v>
       </c>
       <c r="I288" s="2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J288">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K288" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -30970,10 +30970,10 @@
         <v>9.6</v>
       </c>
       <c r="J289">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K289" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290" spans="1:11">
@@ -31002,13 +31002,13 @@
         <v>0</v>
       </c>
       <c r="I290" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J290">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K290" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291" spans="1:11">
@@ -31037,13 +31037,13 @@
         <v>0</v>
       </c>
       <c r="I291" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J291">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K291" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -31072,13 +31072,13 @@
         <v>0</v>
       </c>
       <c r="I292" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J292">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K292" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -31104,13 +31104,13 @@
         <v>0.5</v>
       </c>
       <c r="I293" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J293">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="K293" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/DetalleXDocente20232.xlsx
+++ b/DetalleXDocente20232.xlsx
@@ -21525,16 +21525,19 @@
         <v>23</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I14" s="2">
+        <v>9.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -21554,16 +21557,19 @@
         <v>23</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I15" s="2">
+        <v>9.6</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -22376,16 +22382,19 @@
         <v>25</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H39" s="1">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I39" s="2">
+        <v>9.800000000000001</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -22440,19 +22449,19 @@
         <v>79</v>
       </c>
       <c r="E41">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41" s="1">
-        <v>67.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="H41" s="1">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="I41" s="2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -26402,16 +26411,19 @@
         <v>29</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G156" s="1">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="H156" s="1">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="I156" s="2">
+        <v>8.4</v>
       </c>
       <c r="J156">
         <v>29</v>
@@ -26434,16 +26446,19 @@
         <v>33</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F157">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G157" s="1">
-        <v>0</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H157" s="1">
-        <v>0</v>
+        <v>12.1</v>
+      </c>
+      <c r="I157" s="2">
+        <v>9.4</v>
       </c>
       <c r="J157">
         <v>1</v>
@@ -26463,16 +26478,19 @@
         <v>62</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F158">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G158" s="1">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H158" s="1">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="I158" s="2">
+        <v>8.9</v>
       </c>
       <c r="J158">
         <v>30</v>
@@ -28017,16 +28035,19 @@
         <v>12</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F203">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G203" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H203" s="1">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="I203" s="2">
+        <v>7.5</v>
       </c>
       <c r="J203">
         <v>12</v>
@@ -28116,19 +28137,19 @@
         <v>103</v>
       </c>
       <c r="E206">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F206">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G206" s="1">
-        <v>71.8</v>
+        <v>77.7</v>
       </c>
       <c r="H206" s="1">
-        <v>16.5</v>
+        <v>22.3</v>
       </c>
       <c r="I206" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J206">
         <v>103</v>
@@ -30078,16 +30099,19 @@
         <v>39</v>
       </c>
       <c r="E263">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F263">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G263" s="1">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="H263" s="1">
-        <v>0</v>
+        <v>7.7</v>
+      </c>
+      <c r="I263" s="2">
+        <v>9.6</v>
       </c>
       <c r="J263">
         <v>0</v>
@@ -30110,16 +30134,19 @@
         <v>31</v>
       </c>
       <c r="E264">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F264">
         <v>0</v>
       </c>
       <c r="G264" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H264" s="1">
         <v>0</v>
+      </c>
+      <c r="I264" s="2">
+        <v>10</v>
       </c>
       <c r="J264">
         <v>0</v>
@@ -30142,16 +30169,19 @@
         <v>35</v>
       </c>
       <c r="E265">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F265">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G265" s="1">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H265" s="1">
-        <v>0</v>
+        <v>8.6</v>
+      </c>
+      <c r="I265" s="2">
+        <v>9.6</v>
       </c>
       <c r="J265">
         <v>0</v>
@@ -30174,16 +30204,19 @@
         <v>24</v>
       </c>
       <c r="E266">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F266">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G266" s="1">
-        <v>0</v>
+        <v>95.8</v>
       </c>
       <c r="H266" s="1">
-        <v>0</v>
+        <v>4.2</v>
+      </c>
+      <c r="I266" s="2">
+        <v>9.800000000000001</v>
       </c>
       <c r="J266">
         <v>0</v>
@@ -30206,16 +30239,19 @@
         <v>38</v>
       </c>
       <c r="E267">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G267" s="1">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H267" s="1">
-        <v>0</v>
+        <v>2.6</v>
+      </c>
+      <c r="I267" s="2">
+        <v>9.9</v>
       </c>
       <c r="J267">
         <v>0</v>
@@ -30238,16 +30274,19 @@
         <v>30</v>
       </c>
       <c r="E268">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F268">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G268" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H268" s="1">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="I268" s="2">
+        <v>9</v>
       </c>
       <c r="J268">
         <v>0</v>
@@ -30267,16 +30306,19 @@
         <v>197</v>
       </c>
       <c r="E269">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="F269">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G269" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H269" s="1">
-        <v>0</v>
+        <v>7.1</v>
+      </c>
+      <c r="I269" s="2">
+        <v>9.6</v>
       </c>
       <c r="J269">
         <v>0</v>

--- a/DetalleXDocente20232.xlsx
+++ b/DetalleXDocente20232.xlsx
@@ -25522,25 +25522,25 @@
         <v>29</v>
       </c>
       <c r="E130">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G130" s="1">
-        <v>93.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H130" s="1">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="I130" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J130">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K130" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -25557,25 +25557,25 @@
         <v>31</v>
       </c>
       <c r="E131">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G131" s="1">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="H131" s="1">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="I131" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J131">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K131" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -25729,25 +25729,25 @@
         <v>155</v>
       </c>
       <c r="E136">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F136">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G136" s="1">
-        <v>92.3</v>
+        <v>94.8</v>
       </c>
       <c r="H136" s="1">
-        <v>7.7</v>
+        <v>5.2</v>
       </c>
       <c r="I136" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J136">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K136" s="1">
-        <v>38.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -25983,13 +25983,13 @@
         <v>5.7</v>
       </c>
       <c r="I143" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J143">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K143" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -26015,13 +26015,13 @@
         <v>5.7</v>
       </c>
       <c r="I144" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J144">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K144" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -26411,25 +26411,25 @@
         <v>29</v>
       </c>
       <c r="E156">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F156">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G156" s="1">
-        <v>69</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H156" s="1">
-        <v>31</v>
+        <v>6.9</v>
       </c>
       <c r="I156" s="2">
-        <v>8.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J156">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K156" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -26446,25 +26446,25 @@
         <v>33</v>
       </c>
       <c r="E157">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F157">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G157" s="1">
-        <v>87.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H157" s="1">
-        <v>12.1</v>
+        <v>9.1</v>
       </c>
       <c r="I157" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -26478,25 +26478,25 @@
         <v>62</v>
       </c>
       <c r="E158">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F158">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G158" s="1">
-        <v>79</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H158" s="1">
-        <v>21</v>
+        <v>8.1</v>
       </c>
       <c r="I158" s="2">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="J158">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K158" s="1">
-        <v>48.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -28000,25 +28000,25 @@
         <v>29</v>
       </c>
       <c r="E202">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F202">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G202" s="1">
-        <v>93.09999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="H202" s="1">
-        <v>6.9</v>
+        <v>10.3</v>
       </c>
       <c r="I202" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J202">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K202" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -28035,25 +28035,25 @@
         <v>12</v>
       </c>
       <c r="E203">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F203">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G203" s="1">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="H203" s="1">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="I203" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J203">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K203" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -28070,25 +28070,25 @@
         <v>31</v>
       </c>
       <c r="E204">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F204">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G204" s="1">
-        <v>71</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H204" s="1">
-        <v>29</v>
+        <v>12.9</v>
       </c>
       <c r="I204" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J204">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K204" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -28105,25 +28105,25 @@
         <v>31</v>
       </c>
       <c r="E205">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F205">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G205" s="1">
-        <v>80.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="H205" s="1">
-        <v>19.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I205" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J205">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K205" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -28137,25 +28137,25 @@
         <v>103</v>
       </c>
       <c r="E206">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F206">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G206" s="1">
-        <v>77.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H206" s="1">
-        <v>22.3</v>
+        <v>14.6</v>
       </c>
       <c r="I206" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J206">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="K206" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:11">
